--- a/data/trans_orig/P47A-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P47A-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según su autopercepción del peso respecto de su talla en 2007</t>
+          <t>Población según su autopercepción del peso respecto de su talla en 2007 (tasa de respuesta: 99,78%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10200</t>
+          <t>10783</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>28784</t>
+          <t>27637</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>17478</t>
+          <t>17437</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>39172</t>
+          <t>37585</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>32970</t>
+          <t>31918</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>58337</t>
+          <t>57809</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,18%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>402971</t>
+          <t>404704</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>455805</t>
+          <t>455171</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>58,06%</t>
+          <t>58,31%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>65,68%</t>
+          <t>65,59%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>319611</t>
+          <t>318897</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>369797</t>
+          <t>372092</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>46,43%</t>
+          <t>46,33%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>53,72%</t>
+          <t>54,06%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>738670</t>
+          <t>739893</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>811786</t>
+          <t>810206</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>53,44%</t>
+          <t>53,52%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>58,72%</t>
+          <t>58,61%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>157806</t>
+          <t>157933</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>207382</t>
+          <t>202438</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>22,74%</t>
+          <t>22,76%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>29,88%</t>
+          <t>29,17%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>177153</t>
+          <t>175840</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>222338</t>
+          <t>224365</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>25,74%</t>
+          <t>25,55%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>32,3%</t>
+          <t>32,59%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>348312</t>
+          <t>348064</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>412320</t>
+          <t>411825</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>25,2%</t>
+          <t>25,18%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>29,83%</t>
+          <t>29,79%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>51733</t>
+          <t>51179</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>82517</t>
+          <t>81059</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>98690</t>
+          <t>99020</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>136666</t>
+          <t>137279</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>19,85%</t>
+          <t>19,94%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>158014</t>
+          <t>159219</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>210698</t>
+          <t>209945</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>15,19%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>30984</t>
+          <t>32332</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>57839</t>
+          <t>58390</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>18397</t>
+          <t>19309</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>40411</t>
+          <t>40646</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,9%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,2%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>56777</t>
+          <t>57450</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>90426</t>
+          <t>91660</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,75%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>542962</t>
+          <t>541063</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>601396</t>
+          <t>602412</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>56,45%</t>
+          <t>56,26%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>62,53%</t>
+          <t>62,63%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>471847</t>
+          <t>471600</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>536423</t>
+          <t>535204</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>48,77%</t>
+          <t>48,75%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>55,45%</t>
+          <t>55,32%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1033349</t>
+          <t>1029933</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1121307</t>
+          <t>1116830</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>53,56%</t>
+          <t>53,39%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>58,12%</t>
+          <t>57,89%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>247097</t>
+          <t>246700</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>304448</t>
+          <t>305520</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>25,69%</t>
+          <t>25,65%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>31,65%</t>
+          <t>31,77%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>276579</t>
+          <t>278553</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>337162</t>
+          <t>337014</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>28,59%</t>
+          <t>28,79%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>34,85%</t>
+          <t>34,84%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>542212</t>
+          <t>545026</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>624482</t>
+          <t>622837</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>28,25%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>32,37%</t>
+          <t>32,28%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>56358</t>
+          <t>56256</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>91632</t>
+          <t>90904</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,86%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9,53%</t>
+          <t>9,45%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>108035</t>
+          <t>107417</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>150119</t>
+          <t>149584</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>172949</t>
+          <t>174296</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>228216</t>
+          <t>227768</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>8,96%</t>
+          <t>9,03%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>11,81%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>23538</t>
+          <t>23776</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>47258</t>
+          <t>49917</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>16228</t>
+          <t>15685</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>35908</t>
+          <t>35771</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>45094</t>
+          <t>44657</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>75885</t>
+          <t>76527</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,64%</t>
         </is>
       </c>
     </row>
@@ -1984,12 +1984,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>398944</t>
+          <t>395396</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>448927</t>
+          <t>445273</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1999,12 +1999,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>58,88%</t>
+          <t>58,36%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>66,26%</t>
+          <t>65,72%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>350574</t>
+          <t>347910</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>399324</t>
+          <t>401185</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2034,12 +2034,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>51,54%</t>
+          <t>51,15%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>58,71%</t>
+          <t>58,99%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>756689</t>
+          <t>758637</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>830190</t>
+          <t>831913</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>55,74%</t>
+          <t>55,88%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>61,15%</t>
+          <t>61,28%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>163473</t>
+          <t>163605</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>207864</t>
+          <t>209660</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>24,15%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>30,68%</t>
+          <t>30,95%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>178461</t>
+          <t>176545</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>223398</t>
+          <t>223170</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>26,24%</t>
+          <t>25,96%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>32,85%</t>
+          <t>32,81%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>351754</t>
+          <t>353993</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>419914</t>
+          <t>418981</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>25,91%</t>
+          <t>26,07%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>30,93%</t>
+          <t>30,86%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>26279</t>
+          <t>26246</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>48825</t>
+          <t>50104</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>67556</t>
+          <t>66404</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>100474</t>
+          <t>101195</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,93%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>98743</t>
+          <t>98190</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>140091</t>
+          <t>139851</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,27%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,3%</t>
         </is>
       </c>
     </row>
@@ -2440,12 +2440,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>33369</t>
+          <t>33193</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>59570</t>
+          <t>60897</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,12 +2455,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,49%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2475,12 +2475,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>24973</t>
+          <t>25132</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>47928</t>
+          <t>47558</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,12 +2490,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>64848</t>
+          <t>64642</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>101516</t>
+          <t>101244</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,13%</t>
         </is>
       </c>
     </row>
@@ -2553,12 +2553,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>593646</t>
+          <t>591207</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>647447</t>
+          <t>647853</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,12 +2568,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>63,29%</t>
+          <t>63,03%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>69,03%</t>
+          <t>69,07%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,12 +2588,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>565040</t>
+          <t>565653</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>628833</t>
+          <t>628397</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>54,57%</t>
+          <t>54,63%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>60,73%</t>
+          <t>60,69%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1173890</t>
+          <t>1175429</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1261183</t>
+          <t>1258918</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>59,49%</t>
+          <t>59,57%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>63,91%</t>
+          <t>63,8%</t>
         </is>
       </c>
     </row>
@@ -2666,12 +2666,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>197311</t>
+          <t>195707</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>244820</t>
+          <t>247231</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2681,12 +2681,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>21,04%</t>
+          <t>20,87%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>26,1%</t>
+          <t>26,36%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2701,12 +2701,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>271850</t>
+          <t>272023</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>330898</t>
+          <t>331096</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2716,12 +2716,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>26,26%</t>
+          <t>26,27%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>31,96%</t>
+          <t>31,98%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>482319</t>
+          <t>480364</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>560022</t>
+          <t>558359</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2751,12 +2751,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>24,44%</t>
+          <t>24,34%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>28,38%</t>
+          <t>28,3%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>39637</t>
+          <t>38883</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>66080</t>
+          <t>65846</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>84561</t>
+          <t>83407</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>121622</t>
+          <t>122119</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,79%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>128827</t>
+          <t>133605</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>179760</t>
+          <t>179732</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,7 +2864,7 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,77%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
@@ -3009,12 +3009,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>119808</t>
+          <t>118873</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>167617</t>
+          <t>168226</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3044,12 +3044,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>94447</t>
+          <t>94066</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>138099</t>
+          <t>135634</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3059,12 +3059,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>227742</t>
+          <t>226603</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>289295</t>
+          <t>289730</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,41%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -3122,12 +3122,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1988877</t>
+          <t>1988644</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2095656</t>
+          <t>2093679</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3137,12 +3137,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>60,8%</t>
+          <t>60,79%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>64,06%</t>
+          <t>64,0%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3157,12 +3157,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1761971</t>
+          <t>1766797</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1879394</t>
+          <t>1883197</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3172,12 +3172,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>52,26%</t>
+          <t>52,41%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>55,75%</t>
+          <t>55,86%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3192,12 +3192,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3781441</t>
+          <t>3777222</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3943775</t>
+          <t>3942412</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3207,12 +3207,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>56,86%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>59,37%</t>
+          <t>59,35%</t>
         </is>
       </c>
     </row>
@@ -3235,12 +3235,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>811254</t>
+          <t>814475</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>913150</t>
+          <t>911320</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3250,12 +3250,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>24,9%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>27,91%</t>
+          <t>27,86%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3270,12 +3270,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>953791</t>
+          <t>950884</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1060799</t>
+          <t>1066204</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3285,12 +3285,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>28,29%</t>
+          <t>28,2%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>31,47%</t>
+          <t>31,63%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3305,12 +3305,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1789579</t>
+          <t>1792627</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1942936</t>
+          <t>1941456</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3320,12 +3320,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>26,94%</t>
+          <t>26,99%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>29,25%</t>
+          <t>29,23%</t>
         </is>
       </c>
     </row>
@@ -3348,12 +3348,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>197318</t>
+          <t>197885</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>257772</t>
+          <t>253860</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3363,12 +3363,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>396227</t>
+          <t>389988</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>470841</t>
+          <t>469383</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3398,12 +3398,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>11,75%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>13,97%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>610066</t>
+          <t>606389</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>703342</t>
+          <t>704239</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3433,12 +3433,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,6%</t>
         </is>
       </c>
     </row>
@@ -3615,7 +3615,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según su autopercepción del peso respecto de su talla en 2012</t>
+          <t>Población según su autopercepción del peso respecto de su talla en 2012 (tasa de respuesta: 99,09%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3810,12 +3810,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>17703</t>
+          <t>18675</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>39056</t>
+          <t>40534</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3825,12 +3825,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3845,12 +3845,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>18992</t>
+          <t>18862</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>41079</t>
+          <t>41692</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,09%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3880,12 +3880,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>41575</t>
+          <t>42363</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>72593</t>
+          <t>72223</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,23%</t>
         </is>
       </c>
     </row>
@@ -3923,12 +3923,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>410299</t>
+          <t>410052</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>462757</t>
+          <t>463559</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3938,12 +3938,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>58,93%</t>
+          <t>58,89%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>66,46%</t>
+          <t>66,58%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3958,12 +3958,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>353508</t>
+          <t>356030</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>406965</t>
+          <t>407680</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3973,12 +3973,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>51,64%</t>
+          <t>52,01%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>59,45%</t>
+          <t>59,55%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3993,12 +3993,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>783908</t>
+          <t>782052</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>855592</t>
+          <t>853232</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4008,12 +4008,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>56,77%</t>
+          <t>56,64%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>61,96%</t>
+          <t>61,79%</t>
         </is>
       </c>
     </row>
@@ -4036,12 +4036,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>162705</t>
+          <t>158934</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>210327</t>
+          <t>207071</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4051,12 +4051,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>23,37%</t>
+          <t>22,83%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>30,21%</t>
+          <t>29,74%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>187729</t>
+          <t>185442</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>235468</t>
+          <t>231785</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>27,42%</t>
+          <t>27,09%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>34,4%</t>
+          <t>33,86%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>364752</t>
+          <t>359888</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>432971</t>
+          <t>429556</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>26,06%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>31,36%</t>
+          <t>31,11%</t>
         </is>
       </c>
     </row>
@@ -4149,12 +4149,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>35637</t>
+          <t>36015</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>63634</t>
+          <t>61927</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4164,12 +4164,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>49911</t>
+          <t>49454</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>79460</t>
+          <t>81991</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4199,12 +4199,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,22%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,61%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>89749</t>
+          <t>91389</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>133200</t>
+          <t>130843</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,48%</t>
         </is>
       </c>
     </row>
@@ -4379,12 +4379,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>31939</t>
+          <t>31864</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>57572</t>
+          <t>57589</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>24627</t>
+          <t>23681</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>51378</t>
+          <t>51142</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4429,12 +4429,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>64426</t>
+          <t>63086</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>99114</t>
+          <t>98709</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4464,12 +4464,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,85%</t>
         </is>
       </c>
     </row>
@@ -4492,12 +4492,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>623216</t>
+          <t>621767</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>686778</t>
+          <t>685080</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4507,12 +4507,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>61,71%</t>
+          <t>61,57%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>68,0%</t>
+          <t>67,84%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>506265</t>
+          <t>505633</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>573015</t>
+          <t>572880</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4542,12 +4542,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>49,39%</t>
+          <t>49,33%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>55,9%</t>
+          <t>55,89%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1147024</t>
+          <t>1149026</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1239411</t>
+          <t>1241125</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4577,12 +4577,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>56,37%</t>
+          <t>56,46%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>60,91%</t>
+          <t>60,99%</t>
         </is>
       </c>
     </row>
@@ -4605,12 +4605,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>237567</t>
+          <t>239017</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>298736</t>
+          <t>296441</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4620,12 +4620,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>23,67%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>29,58%</t>
+          <t>29,35%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>318542</t>
+          <t>318267</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>384918</t>
+          <t>382851</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>31,08%</t>
+          <t>31,05%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>37,55%</t>
+          <t>37,35%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>572602</t>
+          <t>575425</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>661374</t>
+          <t>658546</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4690,12 +4690,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>28,14%</t>
+          <t>28,28%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>32,5%</t>
+          <t>32,36%</t>
         </is>
       </c>
     </row>
@@ -4718,12 +4718,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>32883</t>
+          <t>32891</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>60647</t>
+          <t>60113</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4738,7 +4738,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>84568</t>
+          <t>83670</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>124622</t>
+          <t>123993</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4768,12 +4768,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>12,16%</t>
+          <t>12,1%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>123276</t>
+          <t>121964</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>170380</t>
+          <t>173364</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4803,12 +4803,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>8,52%</t>
         </is>
       </c>
     </row>
@@ -4948,12 +4948,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>30652</t>
+          <t>30274</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>57762</t>
+          <t>57199</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4963,12 +4963,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>20522</t>
+          <t>19831</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>42625</t>
+          <t>43416</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4998,12 +4998,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>55139</t>
+          <t>55383</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>91454</t>
+          <t>89854</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5033,12 +5033,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>5,91%</t>
         </is>
       </c>
     </row>
@@ -5061,12 +5061,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>408502</t>
+          <t>412560</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>465549</t>
+          <t>468904</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5076,12 +5076,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>54,42%</t>
+          <t>54,96%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>62,02%</t>
+          <t>62,47%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>324619</t>
+          <t>326534</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>381418</t>
+          <t>384598</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>42,23%</t>
+          <t>42,47%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>49,61%</t>
+          <t>50,03%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>755834</t>
+          <t>755248</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>833506</t>
+          <t>837224</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5146,12 +5146,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>49,75%</t>
+          <t>49,71%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>54,86%</t>
+          <t>55,1%</t>
         </is>
       </c>
     </row>
@@ -5174,12 +5174,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>191888</t>
+          <t>190576</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>242679</t>
+          <t>241264</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5189,12 +5189,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>25,56%</t>
+          <t>25,39%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>32,33%</t>
+          <t>32,14%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5209,12 +5209,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>267160</t>
+          <t>265189</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>322608</t>
+          <t>319529</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5224,12 +5224,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>34,75%</t>
+          <t>34,5%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>41,96%</t>
+          <t>41,56%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5244,12 +5244,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>469888</t>
+          <t>469873</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>547009</t>
+          <t>544256</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5259,12 +5259,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>30,93%</t>
+          <t>30,92%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>36,0%</t>
+          <t>35,82%</t>
         </is>
       </c>
     </row>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>39387</t>
+          <t>38893</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>72424</t>
+          <t>70746</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5302,12 +5302,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,25%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,43%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5322,12 +5322,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>72932</t>
+          <t>74095</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>112044</t>
+          <t>112192</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5337,12 +5337,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,57%</t>
+          <t>14,59%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5357,12 +5357,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>123323</t>
+          <t>120170</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>170259</t>
+          <t>170083</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5372,12 +5372,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,19%</t>
         </is>
       </c>
     </row>
@@ -5517,12 +5517,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>39376</t>
+          <t>38763</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>67281</t>
+          <t>68475</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5532,12 +5532,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,13%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,29%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5552,12 +5552,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>30088</t>
+          <t>30406</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>55354</t>
+          <t>55472</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5567,12 +5567,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5587,12 +5587,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>74448</t>
+          <t>76616</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>113474</t>
+          <t>114615</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5602,12 +5602,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,78%</t>
         </is>
       </c>
     </row>
@@ -5630,12 +5630,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>539331</t>
+          <t>542492</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>602039</t>
+          <t>603457</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5645,12 +5645,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>57,4%</t>
+          <t>57,73%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>64,07%</t>
+          <t>64,22%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5665,12 +5665,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>539288</t>
+          <t>540599</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>602375</t>
+          <t>604770</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5680,12 +5680,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>51,72%</t>
+          <t>51,85%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>57,77%</t>
+          <t>58,0%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5700,12 +5700,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1098965</t>
+          <t>1099317</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1190399</t>
+          <t>1188965</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5715,12 +5715,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>55,44%</t>
+          <t>55,45%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>60,05%</t>
+          <t>59,98%</t>
         </is>
       </c>
     </row>
@@ -5743,12 +5743,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>225487</t>
+          <t>225486</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>284518</t>
+          <t>280470</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5763,7 +5763,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>30,28%</t>
+          <t>29,85%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5778,12 +5778,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>287984</t>
+          <t>289172</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>348299</t>
+          <t>349022</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5793,12 +5793,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>27,62%</t>
+          <t>27,73%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>33,4%</t>
+          <t>33,47%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5813,12 +5813,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>532250</t>
+          <t>531296</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>616173</t>
+          <t>610650</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5828,12 +5828,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>26,85%</t>
+          <t>26,8%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>31,08%</t>
+          <t>30,8%</t>
         </is>
       </c>
     </row>
@@ -5856,12 +5856,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>47876</t>
+          <t>47556</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>83874</t>
+          <t>81349</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5871,12 +5871,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5891,12 +5891,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>90370</t>
+          <t>89370</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>130438</t>
+          <t>130361</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5906,12 +5906,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,67%</t>
+          <t>8,57%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5926,12 +5926,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>149061</t>
+          <t>147786</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>201387</t>
+          <t>202771</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5941,12 +5941,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>10,23%</t>
         </is>
       </c>
     </row>
@@ -6086,12 +6086,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>142634</t>
+          <t>141341</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>194312</t>
+          <t>193665</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6101,12 +6101,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6121,12 +6121,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>112548</t>
+          <t>110608</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>160926</t>
+          <t>159803</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6136,12 +6136,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>4,57%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6156,12 +6156,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>266528</t>
+          <t>268895</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>333897</t>
+          <t>339487</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6171,12 +6171,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,91%</t>
         </is>
       </c>
     </row>
@@ -6199,12 +6199,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2045026</t>
+          <t>2045512</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2165472</t>
+          <t>2161856</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6214,12 +6214,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>60,21%</t>
+          <t>60,23%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>63,76%</t>
+          <t>63,65%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6234,12 +6234,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1785144</t>
+          <t>1793504</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1911584</t>
+          <t>1915111</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6249,12 +6249,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>50,7%</t>
+          <t>50,94%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>54,29%</t>
+          <t>54,39%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6269,12 +6269,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3867229</t>
+          <t>3871049</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4042805</t>
+          <t>4049120</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6284,12 +6284,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>55,9%</t>
+          <t>55,96%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>58,44%</t>
+          <t>58,53%</t>
         </is>
       </c>
     </row>
@@ -6312,12 +6312,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>868813</t>
+          <t>862711</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>976700</t>
+          <t>972558</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6327,12 +6327,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>25,4%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>28,76%</t>
+          <t>28,63%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6347,12 +6347,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1115093</t>
+          <t>1112396</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1232275</t>
+          <t>1226518</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6362,12 +6362,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>31,67%</t>
+          <t>31,59%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>35,0%</t>
+          <t>34,83%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6382,12 +6382,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2009005</t>
+          <t>2006924</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2165331</t>
+          <t>2161969</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6397,12 +6397,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>29,04%</t>
+          <t>29,01%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>31,3%</t>
+          <t>31,25%</t>
         </is>
       </c>
     </row>
@@ -6425,12 +6425,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>180129</t>
+          <t>179266</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>240207</t>
+          <t>242385</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -6440,12 +6440,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,14%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -6460,12 +6460,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>329161</t>
+          <t>331001</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>407350</t>
+          <t>407413</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6475,7 +6475,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -6495,12 +6495,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>529078</t>
+          <t>530625</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>627173</t>
+          <t>626211</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -6510,12 +6510,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,67%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>9,05%</t>
         </is>
       </c>
     </row>
@@ -6692,7 +6692,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según su autopercepción del peso respecto de su talla en 2016</t>
+          <t>Población según su autopercepción del peso respecto de su talla en 2016 (tasa de respuesta: 98,87%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6887,12 +6887,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13072</t>
+          <t>12499</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>33875</t>
+          <t>31290</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6902,12 +6902,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,08%</t>
+          <t>4,69%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6922,12 +6922,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>17628</t>
+          <t>16830</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>36829</t>
+          <t>37780</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6937,12 +6937,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,73%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6957,12 +6957,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>34271</t>
+          <t>33952</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>61187</t>
+          <t>62503</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6972,12 +6972,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,71%</t>
         </is>
       </c>
     </row>
@@ -7000,12 +7000,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>414553</t>
+          <t>417976</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>464491</t>
+          <t>465968</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7015,12 +7015,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>62,16%</t>
+          <t>62,67%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>69,65%</t>
+          <t>69,87%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7035,12 +7035,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>377402</t>
+          <t>376610</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>424702</t>
+          <t>426326</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7050,12 +7050,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>57,19%</t>
+          <t>57,07%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>64,36%</t>
+          <t>64,61%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7070,12 +7070,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>810059</t>
+          <t>807373</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>881381</t>
+          <t>878549</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7085,12 +7085,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>61,05%</t>
+          <t>60,85%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>66,43%</t>
+          <t>66,22%</t>
         </is>
       </c>
     </row>
@@ -7113,12 +7113,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>139563</t>
+          <t>139082</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>184624</t>
+          <t>181193</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7128,82 +7128,82 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>20,85%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
+          <t>27,17%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>174</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>175430</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>154038</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>199422</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>26,59%</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>23,34%</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>30,22%</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>324</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>335688</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>303254</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>367234</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>25,3%</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>22,86%</t>
+        </is>
+      </c>
+      <c r="W6" s="2" t="inlineStr">
+        <is>
           <t>27,68%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>174</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>175430</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>154521</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>197601</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>26,59%</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>23,42%</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>29,95%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>324</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>335688</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>300819</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>369920</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>25,3%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>22,67%</t>
-        </is>
-      </c>
-      <c r="W6" s="2" t="inlineStr">
-        <is>
-          <t>27,88%</t>
         </is>
       </c>
     </row>
@@ -7226,12 +7226,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>32681</t>
+          <t>32310</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>61190</t>
+          <t>59440</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7241,12 +7241,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>43310</t>
+          <t>42059</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>72846</t>
+          <t>71570</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7276,12 +7276,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>10,85%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7296,12 +7296,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>83588</t>
+          <t>83057</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>124094</t>
+          <t>123547</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7311,12 +7311,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,31%</t>
         </is>
       </c>
     </row>
@@ -7456,12 +7456,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>29729</t>
+          <t>30612</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>56113</t>
+          <t>56385</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7471,12 +7471,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,03%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,56%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>27583</t>
+          <t>27936</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>52168</t>
+          <t>51997</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7506,12 +7506,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>63092</t>
+          <t>63741</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>99387</t>
+          <t>99965</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7541,12 +7541,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,9%</t>
         </is>
       </c>
     </row>
@@ -7569,12 +7569,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>624538</t>
+          <t>622640</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>686412</t>
+          <t>689081</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7584,12 +7584,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>61,91%</t>
+          <t>61,73%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>68,05%</t>
+          <t>68,31%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>571697</t>
+          <t>568848</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>636019</t>
+          <t>635906</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7619,12 +7619,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>55,45%</t>
+          <t>55,17%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>61,68%</t>
+          <t>61,67%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1213739</t>
+          <t>1214318</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1303947</t>
+          <t>1302946</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7654,12 +7654,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>59,5%</t>
+          <t>59,53%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>63,92%</t>
+          <t>63,88%</t>
         </is>
       </c>
     </row>
@@ -7682,12 +7682,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>222348</t>
+          <t>220881</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>279670</t>
+          <t>279380</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7697,12 +7697,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>21,9%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>27,72%</t>
+          <t>27,7%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7717,12 +7717,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>278725</t>
+          <t>277940</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>337624</t>
+          <t>341163</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7732,12 +7732,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>27,03%</t>
+          <t>26,96%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>32,74%</t>
+          <t>33,09%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7752,12 +7752,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>515344</t>
+          <t>519039</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>598679</t>
+          <t>597851</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7767,12 +7767,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>25,26%</t>
+          <t>25,45%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>29,35%</t>
+          <t>29,31%</t>
         </is>
       </c>
     </row>
@@ -7795,12 +7795,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>45902</t>
+          <t>44799</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>76633</t>
+          <t>76122</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7810,12 +7810,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7830,12 +7830,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>66460</t>
+          <t>66054</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>101143</t>
+          <t>99842</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,41%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7865,12 +7865,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>117723</t>
+          <t>119742</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>166711</t>
+          <t>169941</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,33%</t>
         </is>
       </c>
     </row>
@@ -8025,12 +8025,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>16259</t>
+          <t>15930</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>37651</t>
+          <t>36638</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8040,12 +8040,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,98%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8060,12 +8060,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>18076</t>
+          <t>18396</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>39395</t>
+          <t>39607</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8075,12 +8075,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8095,12 +8095,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>38437</t>
+          <t>39123</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>69205</t>
+          <t>68923</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8110,12 +8110,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,49%</t>
         </is>
       </c>
     </row>
@@ -8138,12 +8138,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>429465</t>
+          <t>429413</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>486038</t>
+          <t>487007</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8153,12 +8153,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>56,77%</t>
+          <t>56,76%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>64,25%</t>
+          <t>64,37%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -8173,12 +8173,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>425428</t>
+          <t>420957</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>482079</t>
+          <t>477528</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8188,12 +8188,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>54,73%</t>
+          <t>54,15%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>62,01%</t>
+          <t>61,43%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -8208,12 +8208,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>865727</t>
+          <t>865920</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>946722</t>
+          <t>946782</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8223,7 +8223,7 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>56,44%</t>
+          <t>56,45%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
@@ -8251,12 +8251,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>198722</t>
+          <t>197533</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>248364</t>
+          <t>251222</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8266,12 +8266,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>26,27%</t>
+          <t>26,11%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>32,83%</t>
+          <t>33,21%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8286,12 +8286,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>218206</t>
+          <t>220830</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>270437</t>
+          <t>274374</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8301,12 +8301,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>28,07%</t>
+          <t>28,41%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>34,79%</t>
+          <t>35,3%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8321,12 +8321,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>431177</t>
+          <t>436458</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>511745</t>
+          <t>509953</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8336,12 +8336,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>28,11%</t>
+          <t>28,45%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>33,36%</t>
+          <t>33,25%</t>
         </is>
       </c>
     </row>
@@ -8364,12 +8364,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>36935</t>
+          <t>36658</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>64435</t>
+          <t>69031</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8379,12 +8379,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,85%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8399,12 +8399,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>40002</t>
+          <t>40268</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>70639</t>
+          <t>70074</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8414,12 +8414,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8434,12 +8434,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>83176</t>
+          <t>84843</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>126115</t>
+          <t>125172</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8449,12 +8449,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>8,16%</t>
         </is>
       </c>
     </row>
@@ -8594,12 +8594,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>42144</t>
+          <t>40553</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>71013</t>
+          <t>69806</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8609,12 +8609,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,64%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8629,12 +8629,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>30525</t>
+          <t>29897</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>55974</t>
+          <t>55978</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8644,7 +8644,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,96%</t>
+          <t>2,9%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -8664,12 +8664,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>77881</t>
+          <t>79544</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>115796</t>
+          <t>116604</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8679,12 +8679,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,97%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,95%</t>
         </is>
       </c>
     </row>
@@ -8707,12 +8707,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>539608</t>
+          <t>542110</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>601391</t>
+          <t>598319</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8722,12 +8722,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>58,05%</t>
+          <t>58,32%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>64,7%</t>
+          <t>64,37%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8742,12 +8742,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>514791</t>
+          <t>513380</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>579624</t>
+          <t>580159</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8757,12 +8757,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>49,94%</t>
+          <t>49,81%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>56,23%</t>
+          <t>56,29%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8777,12 +8777,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1067088</t>
+          <t>1073934</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1157475</t>
+          <t>1158584</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8792,12 +8792,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>54,44%</t>
+          <t>54,78%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>59,05%</t>
+          <t>59,1%</t>
         </is>
       </c>
     </row>
@@ -8820,12 +8820,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>222129</t>
+          <t>221554</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>276214</t>
+          <t>273166</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -8835,12 +8835,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>23,9%</t>
+          <t>23,83%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>29,72%</t>
+          <t>29,39%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -8855,12 +8855,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>299446</t>
+          <t>300703</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>358838</t>
+          <t>362674</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8870,12 +8870,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>29,05%</t>
+          <t>29,17%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>34,81%</t>
+          <t>35,19%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -8890,12 +8890,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>537521</t>
+          <t>539632</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>621268</t>
+          <t>621545</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -8905,12 +8905,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>27,42%</t>
+          <t>27,53%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>31,69%</t>
+          <t>31,71%</t>
         </is>
       </c>
     </row>
@@ -8933,12 +8933,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>42718</t>
+          <t>43309</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>72624</t>
+          <t>74119</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8948,12 +8948,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,81%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8968,12 +8968,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>94698</t>
+          <t>93980</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>136894</t>
+          <t>136151</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8983,12 +8983,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>9,19%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,28%</t>
+          <t>13,21%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9003,12 +9003,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>148445</t>
+          <t>146131</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>199903</t>
+          <t>198675</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9018,12 +9018,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,2%</t>
+          <t>10,14%</t>
         </is>
       </c>
     </row>
@@ -9163,12 +9163,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>121932</t>
+          <t>119610</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>166901</t>
+          <t>167145</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9178,12 +9178,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9198,12 +9198,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>113246</t>
+          <t>109293</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>158038</t>
+          <t>155227</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9213,12 +9213,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9233,12 +9233,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>245477</t>
+          <t>241408</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>309987</t>
+          <t>309129</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9248,12 +9248,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>4,52%</t>
+          <t>4,51%</t>
         </is>
       </c>
     </row>
@@ -9276,12 +9276,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2072182</t>
+          <t>2066819</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2185687</t>
+          <t>2182858</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9291,12 +9291,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>61,64%</t>
+          <t>61,48%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>65,02%</t>
+          <t>64,93%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9311,12 +9311,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1936621</t>
+          <t>1943146</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2060841</t>
+          <t>2063952</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9326,12 +9326,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>55,35%</t>
+          <t>55,53%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>58,9%</t>
+          <t>58,99%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9346,12 +9346,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4042212</t>
+          <t>4044582</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4209177</t>
+          <t>4213639</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9361,12 +9361,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>58,92%</t>
+          <t>58,95%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>61,35%</t>
+          <t>61,42%</t>
         </is>
       </c>
     </row>
@@ -9389,12 +9389,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>831053</t>
+          <t>827682</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>936277</t>
+          <t>935853</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9404,12 +9404,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>24,72%</t>
+          <t>24,62%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>27,85%</t>
+          <t>27,84%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9424,12 +9424,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1001992</t>
+          <t>1001429</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1110950</t>
+          <t>1109116</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>28,64%</t>
+          <t>28,62%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>31,75%</t>
+          <t>31,7%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9459,12 +9459,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1863089</t>
+          <t>1853909</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2014289</t>
+          <t>2012576</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9474,12 +9474,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>27,16%</t>
+          <t>27,02%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>29,36%</t>
+          <t>29,33%</t>
         </is>
       </c>
     </row>
@@ -9502,12 +9502,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>181817</t>
+          <t>182977</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>240438</t>
+          <t>241334</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -9517,12 +9517,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,44%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -9537,12 +9537,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>274269</t>
+          <t>275515</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>344096</t>
+          <t>343097</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -9552,12 +9552,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,87%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -9572,12 +9572,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>471312</t>
+          <t>473493</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>560778</t>
+          <t>563509</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -9587,12 +9587,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>6,87%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,21%</t>
         </is>
       </c>
     </row>
@@ -9769,7 +9769,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según su autopercepción del peso respecto de su talla en 2023</t>
+          <t>Población según su autopercepción del peso respecto de su talla en 2023 (tasa de respuesta: 99,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9964,12 +9964,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>22180</t>
+          <t>21050</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>61472</t>
+          <t>55423</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9979,12 +9979,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9999,12 +9999,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>24672</t>
+          <t>24337</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>43924</t>
+          <t>43414</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10014,12 +10014,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,52%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>51578</t>
+          <t>53067</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>93949</t>
+          <t>93624</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10049,12 +10049,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,15%</t>
         </is>
       </c>
     </row>
@@ -10077,12 +10077,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>291627</t>
+          <t>293459</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>348799</t>
+          <t>350758</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10092,12 +10092,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>45,89%</t>
+          <t>46,18%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>54,89%</t>
+          <t>55,2%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10112,12 +10112,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>336109</t>
+          <t>334404</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>375717</t>
+          <t>376852</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10127,12 +10127,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>49,89%</t>
+          <t>49,64%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>55,77%</t>
+          <t>55,94%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10147,12 +10147,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>639358</t>
+          <t>643802</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>709752</t>
+          <t>710038</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10162,12 +10162,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>48,84%</t>
+          <t>49,18%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>54,21%</t>
+          <t>54,24%</t>
         </is>
       </c>
     </row>
@@ -10190,12 +10190,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>202824</t>
+          <t>204802</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>260580</t>
+          <t>258742</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10205,12 +10205,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>31,92%</t>
+          <t>32,23%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>41,01%</t>
+          <t>40,72%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -10225,12 +10225,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>209715</t>
+          <t>208699</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>246515</t>
+          <t>249001</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10240,12 +10240,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>31,13%</t>
+          <t>30,98%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>36,59%</t>
+          <t>36,96%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -10260,12 +10260,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>426003</t>
+          <t>425859</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>494216</t>
+          <t>491174</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10275,12 +10275,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>32,54%</t>
+          <t>32,53%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>37,75%</t>
+          <t>37,52%</t>
         </is>
       </c>
     </row>
@@ -10303,12 +10303,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>37020</t>
+          <t>36565</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>62444</t>
+          <t>61474</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -10318,12 +10318,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10338,12 +10338,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>45627</t>
+          <t>46352</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>68491</t>
+          <t>69350</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10353,12 +10353,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,29%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>88582</t>
+          <t>88305</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>122984</t>
+          <t>122372</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,75%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,35%</t>
         </is>
       </c>
     </row>
@@ -10533,12 +10533,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>29789</t>
+          <t>29937</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>80988</t>
+          <t>82263</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10548,12 +10548,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -10568,12 +10568,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>58416</t>
+          <t>59440</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>94534</t>
+          <t>93235</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10583,12 +10583,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -10603,12 +10603,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>84064</t>
+          <t>84925</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>161697</t>
+          <t>160787</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10618,12 +10618,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,48%</t>
         </is>
       </c>
     </row>
@@ -10646,12 +10646,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>290145</t>
+          <t>249197</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>707809</t>
+          <t>705371</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10661,12 +10661,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>24,34%</t>
+          <t>20,9%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>59,38%</t>
+          <t>59,17%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10681,12 +10681,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>523504</t>
+          <t>521587</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>576513</t>
+          <t>574290</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10696,12 +10696,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>54,74%</t>
+          <t>54,54%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>60,28%</t>
+          <t>60,05%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10716,12 +10716,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>747823</t>
+          <t>733175</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1256107</t>
+          <t>1262367</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10731,12 +10731,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>34,81%</t>
+          <t>34,13%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>58,47%</t>
+          <t>58,76%</t>
         </is>
       </c>
     </row>
@@ -10759,12 +10759,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>346023</t>
+          <t>346947</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>836272</t>
+          <t>897713</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10774,12 +10774,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>29,03%</t>
+          <t>29,1%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>70,15%</t>
+          <t>75,31%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>249560</t>
+          <t>253217</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>298880</t>
+          <t>299414</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10809,12 +10809,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>26,09%</t>
+          <t>26,48%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>31,25%</t>
+          <t>31,31%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>621337</t>
+          <t>615312</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1227523</t>
+          <t>1253451</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10844,12 +10844,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>28,92%</t>
+          <t>28,64%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>57,13%</t>
+          <t>58,34%</t>
         </is>
       </c>
     </row>
@@ -10872,12 +10872,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>29442</t>
+          <t>28280</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>79546</t>
+          <t>79089</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10887,12 +10887,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10907,12 +10907,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>46315</t>
+          <t>46298</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>74105</t>
+          <t>73607</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10927,7 +10927,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10942,12 +10942,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>79303</t>
+          <t>77210</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>137388</t>
+          <t>141310</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10957,12 +10957,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,39%</t>
+          <t>6,58%</t>
         </is>
       </c>
     </row>
@@ -11102,12 +11102,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>36182</t>
+          <t>38020</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>71461</t>
+          <t>72736</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11117,12 +11117,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,4%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11137,12 +11137,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>19181</t>
+          <t>19738</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>58416</t>
+          <t>59361</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11152,12 +11152,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11172,12 +11172,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>57585</t>
+          <t>63115</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>120589</t>
+          <t>123724</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11187,12 +11187,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,57%</t>
         </is>
       </c>
     </row>
@@ -11215,12 +11215,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>344832</t>
+          <t>351423</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>410655</t>
+          <t>411580</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11230,12 +11230,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>48,99%</t>
+          <t>49,93%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>58,35%</t>
+          <t>58,48%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -11250,12 +11250,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>530812</t>
+          <t>522124</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>783232</t>
+          <t>767367</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -11265,12 +11265,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>56,98%</t>
+          <t>56,05%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>84,08%</t>
+          <t>82,38%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -11285,12 +11285,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>901102</t>
+          <t>898194</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1250526</t>
+          <t>1214079</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11300,12 +11300,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>55,1%</t>
+          <t>54,92%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>76,47%</t>
+          <t>74,24%</t>
         </is>
       </c>
     </row>
@@ -11328,12 +11328,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>201915</t>
+          <t>201848</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>259992</t>
+          <t>257676</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11343,12 +11343,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>28,69%</t>
+          <t>28,68%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>36,94%</t>
+          <t>36,61%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11363,12 +11363,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>105788</t>
+          <t>115917</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>285822</t>
+          <t>288892</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11378,12 +11378,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,36%</t>
+          <t>12,44%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>30,68%</t>
+          <t>31,01%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11398,12 +11398,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>278488</t>
+          <t>287758</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>524287</t>
+          <t>523499</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11413,12 +11413,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>17,6%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>32,06%</t>
+          <t>32,01%</t>
         </is>
       </c>
     </row>
@@ -11441,12 +11441,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>30322</t>
+          <t>29125</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>57037</t>
+          <t>56475</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11456,12 +11456,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,31%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,1%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11476,12 +11476,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>23196</t>
+          <t>24759</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>68911</t>
+          <t>69652</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11491,12 +11491,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11511,12 +11511,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>59468</t>
+          <t>63814</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>113758</t>
+          <t>115890</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11526,12 +11526,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>7,09%</t>
         </is>
       </c>
     </row>
@@ -11671,12 +11671,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>23887</t>
+          <t>23780</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>54401</t>
+          <t>50669</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11686,12 +11686,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11706,12 +11706,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>33068</t>
+          <t>34375</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>63241</t>
+          <t>65897</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11721,12 +11721,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11741,12 +11741,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>63972</t>
+          <t>65318</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>103153</t>
+          <t>105427</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11756,12 +11756,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,22%</t>
         </is>
       </c>
     </row>
@@ -11784,12 +11784,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>492605</t>
+          <t>492647</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>558523</t>
+          <t>557739</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11799,12 +11799,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>53,2%</t>
+          <t>53,21%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>60,32%</t>
+          <t>60,24%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>590130</t>
+          <t>591481</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>722186</t>
+          <t>729075</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11834,12 +11834,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>53,92%</t>
+          <t>54,04%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>65,98%</t>
+          <t>66,61%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11854,12 +11854,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1107416</t>
+          <t>1106830</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1262670</t>
+          <t>1254379</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11869,12 +11869,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>54,81%</t>
+          <t>54,78%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>62,5%</t>
+          <t>62,09%</t>
         </is>
       </c>
     </row>
@@ -11897,12 +11897,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>255413</t>
+          <t>251107</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>314281</t>
+          <t>308669</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11912,12 +11912,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>27,59%</t>
+          <t>27,12%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>33,94%</t>
+          <t>33,34%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11932,12 +11932,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>254547</t>
+          <t>254529</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>350217</t>
+          <t>347346</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11947,12 +11947,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>23,26%</t>
+          <t>23,25%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>32,0%</t>
+          <t>31,73%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11967,12 +11967,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>525209</t>
+          <t>534718</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>642009</t>
+          <t>645495</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11982,12 +11982,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>26,0%</t>
+          <t>26,47%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>31,78%</t>
+          <t>31,95%</t>
         </is>
       </c>
     </row>
@@ -12010,12 +12010,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>66671</t>
+          <t>67933</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>104680</t>
+          <t>103076</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12025,12 +12025,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,2%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,13%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12045,12 +12045,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>79450</t>
+          <t>77785</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>116351</t>
+          <t>116340</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12060,7 +12060,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -12080,12 +12080,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>153363</t>
+          <t>154225</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>206290</t>
+          <t>207579</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12095,12 +12095,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,63%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,27%</t>
         </is>
       </c>
     </row>
@@ -12240,12 +12240,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>134306</t>
+          <t>133866</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>218038</t>
+          <t>214795</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -12255,12 +12255,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,21%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -12275,12 +12275,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>160228</t>
+          <t>159865</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>229518</t>
+          <t>228000</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -12290,47 +12290,47 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
+          <t>4,37%</t>
+        </is>
+      </c>
+      <c r="P24" s="2" t="inlineStr">
+        <is>
+          <t>6,24%</t>
+        </is>
+      </c>
+      <c r="Q24" s="2" t="inlineStr">
+        <is>
+          <t>401</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr">
+        <is>
+          <t>372222</t>
+        </is>
+      </c>
+      <c r="S24" s="2" t="inlineStr">
+        <is>
+          <t>311437</t>
+        </is>
+      </c>
+      <c r="T24" s="2" t="inlineStr">
+        <is>
+          <t>423865</t>
+        </is>
+      </c>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>5,23%</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
           <t>4,38%</t>
         </is>
       </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>6,28%</t>
-        </is>
-      </c>
-      <c r="Q24" s="2" t="inlineStr">
-        <is>
-          <t>401</t>
-        </is>
-      </c>
-      <c r="R24" s="2" t="inlineStr">
-        <is>
-          <t>372222</t>
-        </is>
-      </c>
-      <c r="S24" s="2" t="inlineStr">
-        <is>
-          <t>310007</t>
-        </is>
-      </c>
-      <c r="T24" s="2" t="inlineStr">
-        <is>
-          <t>422467</t>
-        </is>
-      </c>
-      <c r="U24" s="2" t="inlineStr">
-        <is>
-          <t>5,23%</t>
-        </is>
-      </c>
-      <c r="V24" s="2" t="inlineStr">
-        <is>
-          <t>4,36%</t>
-        </is>
-      </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,96%</t>
         </is>
       </c>
     </row>
@@ -12353,12 +12353,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1384769</t>
+          <t>1374758</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1936999</t>
+          <t>1938435</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12368,12 +12368,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>40,05%</t>
+          <t>39,77%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>56,03%</t>
+          <t>56,07%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12388,12 +12388,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2044004</t>
+          <t>2041502</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2459714</t>
+          <t>2438407</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12403,12 +12403,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>55,91%</t>
+          <t>55,84%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>67,28%</t>
+          <t>66,69%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12423,12 +12423,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3544326</t>
+          <t>3499734</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4219506</t>
+          <t>4217231</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12438,12 +12438,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>49,83%</t>
+          <t>49,2%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>59,32%</t>
+          <t>59,29%</t>
         </is>
       </c>
     </row>
@@ -12466,12 +12466,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1084068</t>
+          <t>1080759</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1739430</t>
+          <t>1784619</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12481,12 +12481,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>31,36%</t>
+          <t>31,26%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>50,31%</t>
+          <t>51,62%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12501,12 +12501,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>835925</t>
+          <t>844955</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1121734</t>
+          <t>1123832</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12516,12 +12516,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>22,86%</t>
+          <t>23,11%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>30,68%</t>
+          <t>30,74%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12536,12 +12536,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2067905</t>
+          <t>2058154</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2874965</t>
+          <t>2854078</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12551,12 +12551,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>29,07%</t>
+          <t>28,93%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>40,42%</t>
+          <t>40,12%</t>
         </is>
       </c>
     </row>
@@ -12579,12 +12579,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>182444</t>
+          <t>176716</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>265578</t>
+          <t>265619</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12594,7 +12594,7 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
@@ -12614,12 +12614,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>218618</t>
+          <t>210900</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>295005</t>
+          <t>295041</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12629,7 +12629,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -12649,12 +12649,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>428323</t>
+          <t>424640</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>548903</t>
+          <t>540172</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -12664,12 +12664,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>7,72%</t>
+          <t>7,59%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P47A-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P47A-Habitat-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>10783</t>
+          <t>10957</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>27637</t>
+          <t>29191</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,58%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>17437</t>
+          <t>17926</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>37585</t>
+          <t>38581</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,46%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>31918</t>
+          <t>31614</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>57809</t>
+          <t>59144</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,28%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>404704</t>
+          <t>400342</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>455171</t>
+          <t>453856</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>58,31%</t>
+          <t>57,69%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>65,59%</t>
+          <t>65,4%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>318897</t>
+          <t>320505</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>372092</t>
+          <t>372290</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>46,33%</t>
+          <t>46,56%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>54,06%</t>
+          <t>54,08%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>739893</t>
+          <t>741430</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>810206</t>
+          <t>812113</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>53,52%</t>
+          <t>53,63%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>58,61%</t>
+          <t>58,75%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>157933</t>
+          <t>159131</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>202438</t>
+          <t>201627</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>22,76%</t>
+          <t>22,93%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>29,17%</t>
+          <t>29,05%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>175840</t>
+          <t>175826</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>224365</t>
+          <t>222052</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>25,55%</t>
+          <t>25,54%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>32,59%</t>
+          <t>32,26%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>348064</t>
+          <t>345223</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>411825</t>
+          <t>410106</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>25,18%</t>
+          <t>24,97%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>29,79%</t>
+          <t>29,67%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>51179</t>
+          <t>53382</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>81059</t>
+          <t>82668</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,91%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>99020</t>
+          <t>96838</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>137279</t>
+          <t>137453</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>19,97%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>159219</t>
+          <t>162573</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>209945</t>
+          <t>211516</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,76%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>15,3%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>32332</t>
+          <t>31783</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>58390</t>
+          <t>59607</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>19309</t>
+          <t>17797</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>40646</t>
+          <t>39507</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>57450</t>
+          <t>55847</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>91660</t>
+          <t>91412</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,74%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>541063</t>
+          <t>537399</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>602412</t>
+          <t>598467</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>56,26%</t>
+          <t>55,87%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>62,63%</t>
+          <t>62,22%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>471600</t>
+          <t>475164</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>535204</t>
+          <t>539411</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>48,75%</t>
+          <t>49,11%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>55,32%</t>
+          <t>55,76%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1029933</t>
+          <t>1034469</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1116830</t>
+          <t>1126266</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>53,39%</t>
+          <t>53,62%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>57,89%</t>
+          <t>58,38%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>246700</t>
+          <t>247195</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>305520</t>
+          <t>306107</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>25,65%</t>
+          <t>25,7%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>31,77%</t>
+          <t>31,83%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>278553</t>
+          <t>278533</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>337014</t>
+          <t>337537</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1583,7 +1583,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>34,84%</t>
+          <t>34,89%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>545026</t>
+          <t>537507</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>622837</t>
+          <t>621278</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>28,25%</t>
+          <t>27,86%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>32,28%</t>
+          <t>32,2%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>56256</t>
+          <t>56521</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>90904</t>
+          <t>90263</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,38%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>107417</t>
+          <t>109168</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>149584</t>
+          <t>151642</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,67%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>174296</t>
+          <t>173313</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>227768</t>
+          <t>227315</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>8,98%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,81%</t>
+          <t>11,78%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>23776</t>
+          <t>24400</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>49917</t>
+          <t>49875</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>15685</t>
+          <t>16019</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>35771</t>
+          <t>35522</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,26%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>44657</t>
+          <t>45651</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>76527</t>
+          <t>76008</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,6%</t>
         </is>
       </c>
     </row>
@@ -1984,12 +1984,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>395396</t>
+          <t>393271</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>445273</t>
+          <t>444476</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1999,12 +1999,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>58,36%</t>
+          <t>58,05%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>65,72%</t>
+          <t>65,6%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2019,12 +2019,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>347910</t>
+          <t>348110</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>401185</t>
+          <t>399042</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2034,12 +2034,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>51,15%</t>
+          <t>51,18%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>58,99%</t>
+          <t>58,67%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2054,12 +2054,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>758637</t>
+          <t>759344</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>831913</t>
+          <t>829430</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>55,88%</t>
+          <t>55,93%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>61,28%</t>
+          <t>61,09%</t>
         </is>
       </c>
     </row>
@@ -2097,12 +2097,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>163605</t>
+          <t>162047</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>209660</t>
+          <t>208790</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2112,12 +2112,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>24,15%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>30,95%</t>
+          <t>30,82%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,12 +2132,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>176545</t>
+          <t>177249</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>223170</t>
+          <t>222303</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2147,12 +2147,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>25,96%</t>
+          <t>26,06%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>32,81%</t>
+          <t>32,69%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,12 +2167,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>353993</t>
+          <t>355221</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>418981</t>
+          <t>418043</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2182,12 +2182,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>26,07%</t>
+          <t>26,16%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>30,86%</t>
+          <t>30,79%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>26246</t>
+          <t>25260</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>50104</t>
+          <t>49196</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,82 +2225,82 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>3,73%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
+          <t>7,26%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>81270</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>66334</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>103236</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>11,95%</t>
+        </is>
+      </c>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>9,75%</t>
+        </is>
+      </c>
+      <c r="P17" s="2" t="inlineStr">
+        <is>
+          <t>15,18%</t>
+        </is>
+      </c>
+      <c r="Q17" s="2" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>117865</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>100468</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>140336</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>8,68%</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
           <t>7,4%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>81270</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>66404</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>101195</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>11,95%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>9,76%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>14,88%</t>
-        </is>
-      </c>
-      <c r="Q17" s="2" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="R17" s="2" t="inlineStr">
-        <is>
-          <t>117865</t>
-        </is>
-      </c>
-      <c r="S17" s="2" t="inlineStr">
-        <is>
-          <t>98190</t>
-        </is>
-      </c>
-      <c r="T17" s="2" t="inlineStr">
-        <is>
-          <t>139851</t>
-        </is>
-      </c>
-      <c r="U17" s="2" t="inlineStr">
-        <is>
-          <t>8,68%</t>
-        </is>
-      </c>
-      <c r="V17" s="2" t="inlineStr">
-        <is>
-          <t>7,23%</t>
-        </is>
-      </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>10,3%</t>
+          <t>10,34%</t>
         </is>
       </c>
     </row>
@@ -2440,12 +2440,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>33193</t>
+          <t>32418</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>60897</t>
+          <t>60889</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,7 +2455,7 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
@@ -2475,12 +2475,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>25132</t>
+          <t>25316</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>47558</t>
+          <t>48720</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2490,12 +2490,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2510,12 +2510,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>64642</t>
+          <t>64526</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>101244</t>
+          <t>101479</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,14%</t>
         </is>
       </c>
     </row>
@@ -2553,12 +2553,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>591207</t>
+          <t>591040</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>647853</t>
+          <t>647736</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2568,12 +2568,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>63,03%</t>
+          <t>63,02%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>69,07%</t>
+          <t>69,06%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2588,12 +2588,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>565653</t>
+          <t>561377</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>628397</t>
+          <t>624041</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>54,63%</t>
+          <t>54,22%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>60,69%</t>
+          <t>60,27%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2623,12 +2623,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1175429</t>
+          <t>1172878</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1258918</t>
+          <t>1261395</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2638,12 +2638,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>59,57%</t>
+          <t>59,44%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>63,8%</t>
+          <t>63,92%</t>
         </is>
       </c>
     </row>
@@ -2666,12 +2666,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>195707</t>
+          <t>197215</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>247231</t>
+          <t>245977</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2681,12 +2681,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>20,87%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>26,36%</t>
+          <t>26,23%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2701,12 +2701,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>272023</t>
+          <t>273078</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>331096</t>
+          <t>332975</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2716,12 +2716,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>26,27%</t>
+          <t>26,37%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>31,98%</t>
+          <t>32,16%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2736,12 +2736,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>480364</t>
+          <t>483052</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>558359</t>
+          <t>564961</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2751,12 +2751,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>24,34%</t>
+          <t>24,48%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>28,3%</t>
+          <t>28,63%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>38883</t>
+          <t>38841</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>65846</t>
+          <t>66678</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2794,12 +2794,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,15%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>83407</t>
+          <t>84289</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>122119</t>
+          <t>125015</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2829,12 +2829,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>11,79%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>133605</t>
+          <t>130862</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>179732</t>
+          <t>179075</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>9,07%</t>
         </is>
       </c>
     </row>
@@ -3009,12 +3009,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>118873</t>
+          <t>116030</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>168226</t>
+          <t>166733</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3024,12 +3024,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3044,12 +3044,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>94066</t>
+          <t>94424</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>135634</t>
+          <t>137985</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3059,12 +3059,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3079,12 +3079,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>226603</t>
+          <t>227694</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>289730</t>
+          <t>289570</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3094,7 +3094,7 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,41%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -3122,12 +3122,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1988644</t>
+          <t>1988561</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2093679</t>
+          <t>2096663</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>64,0%</t>
+          <t>64,09%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3157,12 +3157,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1766797</t>
+          <t>1764177</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1883197</t>
+          <t>1873440</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3172,12 +3172,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>52,41%</t>
+          <t>52,33%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>55,86%</t>
+          <t>55,57%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3192,12 +3192,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3777222</t>
+          <t>3774568</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>3942412</t>
+          <t>3940570</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3207,12 +3207,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>56,86%</t>
+          <t>56,82%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>59,35%</t>
+          <t>59,32%</t>
         </is>
       </c>
     </row>
@@ -3235,12 +3235,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>814475</t>
+          <t>813950</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>911320</t>
+          <t>909062</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3250,12 +3250,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>24,88%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>27,86%</t>
+          <t>27,79%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3270,12 +3270,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>950884</t>
+          <t>961857</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1066204</t>
+          <t>1061237</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3285,12 +3285,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>28,2%</t>
+          <t>28,53%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>31,63%</t>
+          <t>31,48%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3305,12 +3305,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1792627</t>
+          <t>1796744</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1941456</t>
+          <t>1944155</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3320,12 +3320,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>26,99%</t>
+          <t>27,05%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>29,23%</t>
+          <t>29,27%</t>
         </is>
       </c>
     </row>
@@ -3348,12 +3348,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>197885</t>
+          <t>196012</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>253860</t>
+          <t>252900</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3363,12 +3363,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,73%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3383,12 +3383,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>389988</t>
+          <t>392490</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>469383</t>
+          <t>469652</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3398,12 +3398,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3418,12 +3418,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>606389</t>
+          <t>611320</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>704239</t>
+          <t>714762</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3433,12 +3433,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>10,6%</t>
+          <t>10,76%</t>
         </is>
       </c>
     </row>
@@ -3810,12 +3810,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>18675</t>
+          <t>19161</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>40534</t>
+          <t>39085</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3825,12 +3825,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,82%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3845,12 +3845,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>18862</t>
+          <t>18184</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>41692</t>
+          <t>40794</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3880,12 +3880,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>42363</t>
+          <t>43078</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>72223</t>
+          <t>70930</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,14%</t>
         </is>
       </c>
     </row>
@@ -3923,12 +3923,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>410052</t>
+          <t>411255</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>463559</t>
+          <t>461673</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3938,12 +3938,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>58,89%</t>
+          <t>59,07%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>66,58%</t>
+          <t>66,31%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3958,12 +3958,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>356030</t>
+          <t>353878</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>407680</t>
+          <t>409561</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3973,12 +3973,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>52,01%</t>
+          <t>51,7%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>59,55%</t>
+          <t>59,83%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3993,12 +3993,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>782052</t>
+          <t>782795</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>853232</t>
+          <t>857243</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4008,12 +4008,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>56,64%</t>
+          <t>56,69%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>61,79%</t>
+          <t>62,08%</t>
         </is>
       </c>
     </row>
@@ -4036,12 +4036,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>158934</t>
+          <t>161372</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>207071</t>
+          <t>208257</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4051,12 +4051,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>23,18%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>29,74%</t>
+          <t>29,91%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>185442</t>
+          <t>187377</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>231785</t>
+          <t>237138</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4086,12 +4086,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>27,09%</t>
+          <t>27,37%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>33,86%</t>
+          <t>34,64%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>359888</t>
+          <t>360636</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>429556</t>
+          <t>428902</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4121,12 +4121,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>26,12%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>31,11%</t>
+          <t>31,06%</t>
         </is>
       </c>
     </row>
@@ -4149,12 +4149,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>36015</t>
+          <t>36315</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>61927</t>
+          <t>61319</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4164,12 +4164,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,22%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>49454</t>
+          <t>49444</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>81991</t>
+          <t>80175</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4204,7 +4204,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>11,98%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>91389</t>
+          <t>91546</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>130843</t>
+          <t>132852</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4234,12 +4234,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,48%</t>
+          <t>9,62%</t>
         </is>
       </c>
     </row>
@@ -4379,12 +4379,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>31864</t>
+          <t>32313</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>57589</t>
+          <t>58937</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -4394,12 +4394,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,16%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>23681</t>
+          <t>24506</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>51142</t>
+          <t>50819</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4429,12 +4429,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>63086</t>
+          <t>63574</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>98709</t>
+          <t>99398</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -4464,12 +4464,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,88%</t>
         </is>
       </c>
     </row>
@@ -4492,12 +4492,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>621767</t>
+          <t>621815</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>685080</t>
+          <t>686749</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4512,7 +4512,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>67,84%</t>
+          <t>68,0%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>505633</t>
+          <t>501279</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>572880</t>
+          <t>570686</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4542,12 +4542,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>49,33%</t>
+          <t>48,9%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>55,89%</t>
+          <t>55,67%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1149026</t>
+          <t>1149295</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1241125</t>
+          <t>1243117</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4577,12 +4577,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>56,46%</t>
+          <t>56,48%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>60,99%</t>
+          <t>61,09%</t>
         </is>
       </c>
     </row>
@@ -4605,12 +4605,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>239017</t>
+          <t>238024</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>296441</t>
+          <t>297440</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4620,12 +4620,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>23,67%</t>
+          <t>23,57%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>29,35%</t>
+          <t>29,45%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>318267</t>
+          <t>315968</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>382851</t>
+          <t>380659</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>31,05%</t>
+          <t>30,82%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>37,35%</t>
+          <t>37,13%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>575425</t>
+          <t>568796</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>658546</t>
+          <t>655109</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4690,12 +4690,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>28,28%</t>
+          <t>27,95%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>32,36%</t>
+          <t>32,19%</t>
         </is>
       </c>
     </row>
@@ -4718,12 +4718,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>32891</t>
+          <t>32166</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>60113</t>
+          <t>58979</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4733,12 +4733,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,19%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>83670</t>
+          <t>83834</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>123993</t>
+          <t>122952</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4768,12 +4768,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,18%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>11,99%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>121964</t>
+          <t>123107</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>173364</t>
+          <t>174508</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4803,12 +4803,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,05%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,52%</t>
+          <t>8,58%</t>
         </is>
       </c>
     </row>
@@ -4948,12 +4948,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>30274</t>
+          <t>31220</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>57199</t>
+          <t>57716</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4963,12 +4963,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>19831</t>
+          <t>20625</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>43416</t>
+          <t>43515</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4998,12 +4998,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>55383</t>
+          <t>56939</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>89854</t>
+          <t>90910</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5033,12 +5033,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,98%</t>
         </is>
       </c>
     </row>
@@ -5061,12 +5061,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>412560</t>
+          <t>412117</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>468904</t>
+          <t>466580</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5076,12 +5076,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>54,96%</t>
+          <t>54,9%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>62,47%</t>
+          <t>62,16%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>326534</t>
+          <t>324649</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>384598</t>
+          <t>381541</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>42,47%</t>
+          <t>42,23%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>50,03%</t>
+          <t>49,63%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>755248</t>
+          <t>755020</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>837224</t>
+          <t>834242</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5146,12 +5146,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>49,71%</t>
+          <t>49,69%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>55,1%</t>
+          <t>54,91%</t>
         </is>
       </c>
     </row>
@@ -5174,12 +5174,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>190576</t>
+          <t>190582</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>241264</t>
+          <t>239877</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5194,7 +5194,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>32,14%</t>
+          <t>31,96%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5209,12 +5209,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>265189</t>
+          <t>268241</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>319529</t>
+          <t>324804</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5224,12 +5224,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>34,5%</t>
+          <t>34,89%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>41,56%</t>
+          <t>42,25%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5244,12 +5244,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>469873</t>
+          <t>472383</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>544256</t>
+          <t>548499</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5259,12 +5259,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>30,92%</t>
+          <t>31,09%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>35,82%</t>
+          <t>36,1%</t>
         </is>
       </c>
     </row>
@@ -5287,12 +5287,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>38893</t>
+          <t>40722</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>70746</t>
+          <t>72610</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5302,12 +5302,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5322,12 +5322,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>74095</t>
+          <t>74711</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>112192</t>
+          <t>112170</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5337,7 +5337,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -5357,12 +5357,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>120170</t>
+          <t>121358</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>170083</t>
+          <t>171214</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5372,12 +5372,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>7,91%</t>
+          <t>7,99%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>11,27%</t>
         </is>
       </c>
     </row>
@@ -5517,12 +5517,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>38763</t>
+          <t>36875</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>68475</t>
+          <t>65801</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5532,12 +5532,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,0%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5552,12 +5552,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>30406</t>
+          <t>30946</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>55472</t>
+          <t>57605</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5567,12 +5567,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,97%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5587,12 +5587,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>76616</t>
+          <t>75786</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>114615</t>
+          <t>115772</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5602,12 +5602,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,84%</t>
         </is>
       </c>
     </row>
@@ -5630,12 +5630,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>542492</t>
+          <t>542473</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>603457</t>
+          <t>603397</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5650,7 +5650,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>64,22%</t>
+          <t>64,21%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5665,12 +5665,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>540599</t>
+          <t>537771</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>604770</t>
+          <t>606657</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5680,12 +5680,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>51,85%</t>
+          <t>51,57%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>58,0%</t>
+          <t>58,18%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5700,12 +5700,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1099317</t>
+          <t>1095941</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1188965</t>
+          <t>1185524</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5715,12 +5715,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>55,45%</t>
+          <t>55,28%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>59,98%</t>
+          <t>59,8%</t>
         </is>
       </c>
     </row>
@@ -5743,12 +5743,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>225486</t>
+          <t>225142</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>280470</t>
+          <t>281549</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5758,12 +5758,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>23,96%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>29,85%</t>
+          <t>29,96%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5778,12 +5778,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>289172</t>
+          <t>290138</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>349022</t>
+          <t>350145</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5793,12 +5793,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>27,73%</t>
+          <t>27,83%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>33,47%</t>
+          <t>33,58%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5813,12 +5813,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>531296</t>
+          <t>532825</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>610650</t>
+          <t>609521</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5828,12 +5828,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>26,8%</t>
+          <t>26,88%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
+          <t>30,75%</t>
         </is>
       </c>
     </row>
@@ -5856,12 +5856,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>47556</t>
+          <t>46998</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>81349</t>
+          <t>78576</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5871,12 +5871,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,36%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5891,12 +5891,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>89370</t>
+          <t>91105</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>130361</t>
+          <t>132404</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5906,12 +5906,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,74%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5926,12 +5926,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>147786</t>
+          <t>147089</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>202771</t>
+          <t>199384</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5941,12 +5941,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>10,06%</t>
         </is>
       </c>
     </row>
@@ -6086,12 +6086,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>141341</t>
+          <t>141203</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>193665</t>
+          <t>192392</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6106,7 +6106,7 @@
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,66%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6121,12 +6121,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>110608</t>
+          <t>111624</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>159803</t>
+          <t>158766</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6136,12 +6136,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6156,12 +6156,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>268895</t>
+          <t>267764</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>339487</t>
+          <t>339602</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6171,7 +6171,7 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2045512</t>
+          <t>2045023</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2161856</t>
+          <t>2162717</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6214,12 +6214,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>60,23%</t>
+          <t>60,21%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>63,65%</t>
+          <t>63,68%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6234,12 +6234,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1793504</t>
+          <t>1780881</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>1915111</t>
+          <t>1904876</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6249,12 +6249,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>50,94%</t>
+          <t>50,58%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>54,39%</t>
+          <t>54,1%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6269,12 +6269,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3871049</t>
+          <t>3865005</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4049120</t>
+          <t>4032176</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6284,12 +6284,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>55,96%</t>
+          <t>55,87%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>58,53%</t>
+          <t>58,29%</t>
         </is>
       </c>
     </row>
@@ -6312,12 +6312,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>862711</t>
+          <t>866054</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>972558</t>
+          <t>965255</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6327,12 +6327,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>25,4%</t>
+          <t>25,5%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>28,63%</t>
+          <t>28,42%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6347,12 +6347,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1112396</t>
+          <t>1114744</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1226518</t>
+          <t>1228494</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6362,12 +6362,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>31,59%</t>
+          <t>31,66%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>34,83%</t>
+          <t>34,89%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6382,12 +6382,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2006924</t>
+          <t>2008816</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2161969</t>
+          <t>2162024</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6397,7 +6397,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>29,01%</t>
+          <t>29,04%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -6425,12 +6425,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>179266</t>
+          <t>177661</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>242385</t>
+          <t>239646</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -6440,12 +6440,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>5,28%</t>
+          <t>5,23%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,06%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -6460,12 +6460,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>331001</t>
+          <t>330774</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>407413</t>
+          <t>408016</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6475,12 +6475,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>9,4%</t>
+          <t>9,39%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -6495,12 +6495,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>530625</t>
+          <t>532162</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>626211</t>
+          <t>626882</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -6510,12 +6510,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>7,67%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>9,06%</t>
         </is>
       </c>
     </row>
@@ -6887,12 +6887,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>12499</t>
+          <t>12873</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>31290</t>
+          <t>30327</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6902,12 +6902,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>4,55%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6922,12 +6922,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16830</t>
+          <t>16926</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>37780</t>
+          <t>36006</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6937,12 +6937,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6957,12 +6957,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>33952</t>
+          <t>34263</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>62503</t>
+          <t>62428</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6972,7 +6972,7 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
@@ -7000,12 +7000,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>417976</t>
+          <t>415707</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>465968</t>
+          <t>467731</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7015,12 +7015,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>62,67%</t>
+          <t>62,33%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>69,87%</t>
+          <t>70,13%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7035,12 +7035,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>376610</t>
+          <t>376622</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>426326</t>
+          <t>426044</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7055,7 +7055,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>64,61%</t>
+          <t>64,56%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7070,12 +7070,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>807373</t>
+          <t>808506</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>878549</t>
+          <t>877171</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7085,12 +7085,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>60,85%</t>
+          <t>60,94%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>66,22%</t>
+          <t>66,11%</t>
         </is>
       </c>
     </row>
@@ -7113,12 +7113,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>139082</t>
+          <t>136807</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>181193</t>
+          <t>186027</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7128,12 +7128,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>20,85%</t>
+          <t>20,51%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>27,17%</t>
+          <t>27,89%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7148,12 +7148,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>154038</t>
+          <t>153340</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>199422</t>
+          <t>199264</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7163,12 +7163,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>23,34%</t>
+          <t>23,24%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>30,22%</t>
+          <t>30,2%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7183,12 +7183,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>303254</t>
+          <t>303766</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>367234</t>
+          <t>366522</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7198,12 +7198,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>22,86%</t>
+          <t>22,89%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>27,68%</t>
+          <t>27,62%</t>
         </is>
       </c>
     </row>
@@ -7226,12 +7226,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>32310</t>
+          <t>33673</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>59440</t>
+          <t>60727</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7241,12 +7241,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>42059</t>
+          <t>43896</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>71570</t>
+          <t>73740</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7276,12 +7276,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7296,12 +7296,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>83057</t>
+          <t>82084</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>123547</t>
+          <t>122270</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7311,12 +7311,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,22%</t>
         </is>
       </c>
     </row>
@@ -7456,12 +7456,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>30612</t>
+          <t>30945</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>56385</t>
+          <t>58283</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -7471,12 +7471,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>27936</t>
+          <t>28673</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>51997</t>
+          <t>51722</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -7506,12 +7506,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,78%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>63741</t>
+          <t>64416</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>99965</t>
+          <t>99907</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -7541,7 +7541,7 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
@@ -7569,12 +7569,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>622640</t>
+          <t>625953</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>689081</t>
+          <t>685131</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7584,82 +7584,82 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
+          <t>62,05%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>67,92%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>570</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>603360</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>573305</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>637337</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>58,52%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>55,6%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>61,81%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>1182</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>1259138</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>1215260</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>1302280</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
           <t>61,73%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>68,31%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>570</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>603360</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>568848</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>635906</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>58,52%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>55,17%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>61,67%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1182</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>1259138</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>1214318</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>1302946</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>61,73%</t>
-        </is>
-      </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>59,53%</t>
+          <t>59,58%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>63,88%</t>
+          <t>63,84%</t>
         </is>
       </c>
     </row>
@@ -7682,12 +7682,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>220881</t>
+          <t>224607</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>279380</t>
+          <t>279183</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7697,12 +7697,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>22,27%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>27,7%</t>
+          <t>27,68%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7717,12 +7717,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>277940</t>
+          <t>276887</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>341163</t>
+          <t>334936</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7732,12 +7732,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>26,96%</t>
+          <t>26,85%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>33,09%</t>
+          <t>32,48%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7752,12 +7752,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>519039</t>
+          <t>515931</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>597851</t>
+          <t>599015</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7767,12 +7767,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>25,45%</t>
+          <t>25,29%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>29,31%</t>
+          <t>29,37%</t>
         </is>
       </c>
     </row>
@@ -7795,12 +7795,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>44799</t>
+          <t>44332</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>76122</t>
+          <t>75979</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7810,12 +7810,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,53%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7830,12 +7830,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>66054</t>
+          <t>66556</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>99842</t>
+          <t>102979</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7845,12 +7845,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,99%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7865,12 +7865,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>119742</t>
+          <t>118782</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>169941</t>
+          <t>167199</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7880,12 +7880,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,2%</t>
         </is>
       </c>
     </row>
@@ -8025,12 +8025,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>15930</t>
+          <t>15630</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>36638</t>
+          <t>36601</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8040,7 +8040,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>2,11%</t>
+          <t>2,07%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -8060,12 +8060,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>18396</t>
+          <t>19028</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>39607</t>
+          <t>39767</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8075,12 +8075,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>5,1%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8095,12 +8095,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>39123</t>
+          <t>40286</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>68923</t>
+          <t>69363</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8110,12 +8110,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>4,49%</t>
+          <t>4,52%</t>
         </is>
       </c>
     </row>
@@ -8138,12 +8138,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>429413</t>
+          <t>431187</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>487007</t>
+          <t>486084</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8153,12 +8153,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>56,76%</t>
+          <t>57,0%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>64,37%</t>
+          <t>64,25%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -8173,12 +8173,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>420957</t>
+          <t>420936</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>477528</t>
+          <t>476476</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8193,7 +8193,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>61,43%</t>
+          <t>61,29%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -8208,12 +8208,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>865920</t>
+          <t>864799</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>946782</t>
+          <t>945633</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>56,45%</t>
+          <t>56,38%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>61,72%</t>
+          <t>61,65%</t>
         </is>
       </c>
     </row>
@@ -8251,12 +8251,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>197533</t>
+          <t>196831</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>251222</t>
+          <t>246997</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8266,12 +8266,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>26,11%</t>
+          <t>26,02%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>33,21%</t>
+          <t>32,65%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8286,12 +8286,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>220830</t>
+          <t>220142</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>274374</t>
+          <t>272080</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8301,12 +8301,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>28,41%</t>
+          <t>28,32%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>35,3%</t>
+          <t>35,0%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8321,12 +8321,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>436458</t>
+          <t>435907</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>509953</t>
+          <t>510483</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8336,12 +8336,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>28,45%</t>
+          <t>28,42%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>33,25%</t>
+          <t>33,28%</t>
         </is>
       </c>
     </row>
@@ -8364,12 +8364,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>36658</t>
+          <t>35809</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>69031</t>
+          <t>65302</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8379,12 +8379,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,85%</t>
+          <t>4,73%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8399,12 +8399,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>40268</t>
+          <t>41512</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>70074</t>
+          <t>70639</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8414,12 +8414,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,34%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>9,09%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8434,12 +8434,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>84843</t>
+          <t>84753</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>125172</t>
+          <t>126429</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8454,7 +8454,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,24%</t>
         </is>
       </c>
     </row>
@@ -8594,12 +8594,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>40553</t>
+          <t>41080</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>69806</t>
+          <t>70098</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8609,12 +8609,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,54%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8629,12 +8629,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>29897</t>
+          <t>29572</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>55978</t>
+          <t>55124</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8644,12 +8644,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8664,12 +8664,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>79544</t>
+          <t>78866</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>116604</t>
+          <t>118267</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8679,12 +8679,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>6,03%</t>
         </is>
       </c>
     </row>
@@ -8707,12 +8707,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>542110</t>
+          <t>536474</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>598319</t>
+          <t>595481</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8722,12 +8722,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>58,32%</t>
+          <t>57,71%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>64,37%</t>
+          <t>64,06%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8742,12 +8742,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>513380</t>
+          <t>511616</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>580159</t>
+          <t>579465</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8757,12 +8757,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>49,81%</t>
+          <t>49,64%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>56,29%</t>
+          <t>56,22%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8777,12 +8777,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1073934</t>
+          <t>1069452</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1158584</t>
+          <t>1162108</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8792,12 +8792,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>54,78%</t>
+          <t>54,56%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>59,1%</t>
+          <t>59,28%</t>
         </is>
       </c>
     </row>
@@ -8820,12 +8820,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>221554</t>
+          <t>222211</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>273166</t>
+          <t>275673</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -8835,12 +8835,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>23,83%</t>
+          <t>23,91%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>29,39%</t>
+          <t>29,66%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -8855,12 +8855,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>300703</t>
+          <t>300316</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>362674</t>
+          <t>359983</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -8870,12 +8870,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>29,17%</t>
+          <t>29,14%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>35,19%</t>
+          <t>34,92%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -8890,12 +8890,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>539632</t>
+          <t>535533</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>621545</t>
+          <t>619834</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -8905,12 +8905,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>27,53%</t>
+          <t>27,32%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>31,71%</t>
+          <t>31,62%</t>
         </is>
       </c>
     </row>
@@ -8933,12 +8933,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>43309</t>
+          <t>43043</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>74119</t>
+          <t>74003</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8948,12 +8948,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>4,66%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,97%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8968,12 +8968,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>93980</t>
+          <t>94716</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>136151</t>
+          <t>135040</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8983,12 +8983,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,19%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9003,12 +9003,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>146131</t>
+          <t>144412</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>198675</t>
+          <t>195280</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9018,12 +9018,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>9,96%</t>
         </is>
       </c>
     </row>
@@ -9163,12 +9163,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>119610</t>
+          <t>119323</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>167145</t>
+          <t>168350</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -9178,12 +9178,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -9198,12 +9198,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>109293</t>
+          <t>113416</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>155227</t>
+          <t>156670</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -9213,12 +9213,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -9233,12 +9233,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>241408</t>
+          <t>242466</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>309129</t>
+          <t>310983</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9248,12 +9248,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,53%</t>
         </is>
       </c>
     </row>
@@ -9276,12 +9276,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2066819</t>
+          <t>2069852</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2182858</t>
+          <t>2180276</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9291,12 +9291,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>61,48%</t>
+          <t>61,57%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>64,93%</t>
+          <t>64,86%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9311,12 +9311,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>1943146</t>
+          <t>1943328</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2063952</t>
+          <t>2063720</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9326,12 +9326,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>55,53%</t>
+          <t>55,54%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>58,99%</t>
+          <t>58,98%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9346,12 +9346,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>4044582</t>
+          <t>4050934</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4213639</t>
+          <t>4212016</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9361,12 +9361,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>58,95%</t>
+          <t>59,04%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>61,42%</t>
+          <t>61,39%</t>
         </is>
       </c>
     </row>
@@ -9389,12 +9389,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>827682</t>
+          <t>833729</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>935853</t>
+          <t>935603</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9404,12 +9404,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>24,62%</t>
+          <t>24,8%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>27,84%</t>
+          <t>27,83%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9424,12 +9424,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1001429</t>
+          <t>999393</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1109116</t>
+          <t>1110330</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9439,12 +9439,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>28,62%</t>
+          <t>28,56%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>31,7%</t>
+          <t>31,73%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9459,12 +9459,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1853909</t>
+          <t>1870447</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2012576</t>
+          <t>2020499</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9474,12 +9474,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>27,02%</t>
+          <t>27,26%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>29,33%</t>
+          <t>29,45%</t>
         </is>
       </c>
     </row>
@@ -9502,12 +9502,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>182977</t>
+          <t>181943</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>241334</t>
+          <t>242073</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -9517,12 +9517,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>5,44%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,2%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -9537,12 +9537,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>275515</t>
+          <t>271762</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>343097</t>
+          <t>345397</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -9552,12 +9552,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -9572,12 +9572,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>473493</t>
+          <t>471554</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>563509</t>
+          <t>560275</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -9587,12 +9587,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,87%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>8,17%</t>
         </is>
       </c>
     </row>
@@ -9959,32 +9959,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>35475</t>
+          <t>34969</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>21050</t>
+          <t>22528</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>55423</t>
+          <t>53090</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,26%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9994,32 +9994,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>33139</t>
+          <t>34716</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>24337</t>
+          <t>25933</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>43414</t>
+          <t>45813</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10029,32 +10029,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>68613</t>
+          <t>69684</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>53067</t>
+          <t>54636</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>93624</t>
+          <t>90298</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>6,35%</t>
         </is>
       </c>
     </row>
@@ -10072,32 +10072,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>322889</t>
+          <t>362026</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>293459</t>
+          <t>331994</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>350758</t>
+          <t>390375</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>50,81%</t>
+          <t>52,41%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>46,18%</t>
+          <t>48,07%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>55,2%</t>
+          <t>56,52%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10107,32 +10107,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>355474</t>
+          <t>390962</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>334404</t>
+          <t>369269</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>376852</t>
+          <t>415635</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>52,76%</t>
+          <t>53,48%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>49,64%</t>
+          <t>50,52%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>55,94%</t>
+          <t>56,86%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10142,32 +10142,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>678363</t>
+          <t>752988</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>643802</t>
+          <t>717286</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>710038</t>
+          <t>788693</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>51,82%</t>
+          <t>52,96%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>49,18%</t>
+          <t>50,45%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>54,24%</t>
+          <t>55,48%</t>
         </is>
       </c>
     </row>
@@ -10185,32 +10185,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>228995</t>
+          <t>241598</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>204802</t>
+          <t>215589</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>258742</t>
+          <t>269901</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>36,04%</t>
+          <t>34,98%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>32,23%</t>
+          <t>31,21%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>40,72%</t>
+          <t>39,08%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -10220,32 +10220,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>228277</t>
+          <t>245940</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>208699</t>
+          <t>224102</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>249001</t>
+          <t>264490</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>33,88%</t>
+          <t>33,65%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>30,98%</t>
+          <t>30,66%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>36,96%</t>
+          <t>36,18%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -10255,32 +10255,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>457272</t>
+          <t>487538</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>425859</t>
+          <t>453736</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>491174</t>
+          <t>524141</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>34,93%</t>
+          <t>34,29%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>32,53%</t>
+          <t>31,92%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>37,52%</t>
+          <t>36,87%</t>
         </is>
       </c>
     </row>
@@ -10298,32 +10298,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>48083</t>
+          <t>52117</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>36565</t>
+          <t>39415</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>61474</t>
+          <t>66705</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,55%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>9,67%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10333,32 +10333,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>56818</t>
+          <t>59363</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>46352</t>
+          <t>48626</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>69350</t>
+          <t>73090</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,29%</t>
+          <t>10,0%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10368,32 +10368,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>104900</t>
+          <t>111480</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>88305</t>
+          <t>94851</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>122372</t>
+          <t>129879</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>6,75%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,35%</t>
+          <t>9,14%</t>
         </is>
       </c>
     </row>
@@ -10411,17 +10411,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>635441</t>
+          <t>690710</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10446,17 +10446,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>673707</t>
+          <t>730982</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>673707</t>
+          <t>730982</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>673707</t>
+          <t>730982</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10481,17 +10481,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1309148</t>
+          <t>1421691</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1309148</t>
+          <t>1421691</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1309148</t>
+          <t>1421691</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10528,32 +10528,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>54776</t>
+          <t>60183</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>29937</t>
+          <t>43843</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>82263</t>
+          <t>85817</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>8,19%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -10563,32 +10563,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>73943</t>
+          <t>80289</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>59440</t>
+          <t>63861</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>93235</t>
+          <t>100644</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>7,73%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>6,22%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -10598,32 +10598,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>128719</t>
+          <t>140472</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>84925</t>
+          <t>113536</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>160787</t>
+          <t>169340</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>5,36%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>8,0%</t>
         </is>
       </c>
     </row>
@@ -10641,32 +10641,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>550948</t>
+          <t>624502</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>249197</t>
+          <t>588345</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>705371</t>
+          <t>659627</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>46,22%</t>
+          <t>59,59%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>20,9%</t>
+          <t>56,14%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>59,17%</t>
+          <t>62,94%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10676,32 +10676,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>550461</t>
+          <t>613239</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>521587</t>
+          <t>585832</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>574290</t>
+          <t>642573</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>57,56%</t>
+          <t>57,37%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>54,54%</t>
+          <t>54,81%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>60,05%</t>
+          <t>60,11%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10711,32 +10711,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>1101409</t>
+          <t>1237742</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>733175</t>
+          <t>1190936</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1262367</t>
+          <t>1283940</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>51,26%</t>
+          <t>58,47%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>34,13%</t>
+          <t>56,26%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>58,76%</t>
+          <t>60,65%</t>
         </is>
       </c>
     </row>
@@ -10754,32 +10754,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>530464</t>
+          <t>301238</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>346947</t>
+          <t>264049</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>897713</t>
+          <t>332215</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>44,5%</t>
+          <t>28,74%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>29,1%</t>
+          <t>25,2%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>75,31%</t>
+          <t>31,7%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10789,32 +10789,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>273774</t>
+          <t>309753</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>253217</t>
+          <t>284457</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>299414</t>
+          <t>336920</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>28,63%</t>
+          <t>28,98%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>26,48%</t>
+          <t>26,61%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>31,31%</t>
+          <t>31,52%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10824,32 +10824,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>804238</t>
+          <t>610991</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>615312</t>
+          <t>565725</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1253451</t>
+          <t>653153</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>37,43%</t>
+          <t>28,86%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>28,64%</t>
+          <t>26,72%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>58,34%</t>
+          <t>30,85%</t>
         </is>
       </c>
     </row>
@@ -10867,32 +10867,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>55886</t>
+          <t>62073</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>28280</t>
+          <t>47535</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>79089</t>
+          <t>79513</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>4,69%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>6,63%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10902,32 +10902,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>58213</t>
+          <t>65656</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>46298</t>
+          <t>53324</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>73607</t>
+          <t>81424</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>6,09%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>7,7%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10937,32 +10937,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>114100</t>
+          <t>127729</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>77210</t>
+          <t>107916</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>141310</t>
+          <t>152515</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>6,03%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>7,2%</t>
         </is>
       </c>
     </row>
@@ -10980,17 +10980,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1192074</t>
+          <t>1047996</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1192074</t>
+          <t>1047996</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1192074</t>
+          <t>1047996</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11015,17 +11015,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>956391</t>
+          <t>1068938</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>956391</t>
+          <t>1068938</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>956391</t>
+          <t>1068938</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11050,17 +11050,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>2148465</t>
+          <t>2116934</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>2148465</t>
+          <t>2116934</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>2148465</t>
+          <t>2116934</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11097,32 +11097,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>52348</t>
+          <t>56586</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>38020</t>
+          <t>41255</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>72736</t>
+          <t>77838</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>10,33%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11132,32 +11132,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>40437</t>
+          <t>49282</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>19738</t>
+          <t>37516</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>59361</t>
+          <t>64211</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>6,08%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11167,32 +11167,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>92785</t>
+          <t>105868</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>63115</t>
+          <t>84797</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>123724</t>
+          <t>130344</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>5,67%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>3,86%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>8,08%</t>
         </is>
       </c>
     </row>
@@ -11210,32 +11210,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>381613</t>
+          <t>437829</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>351423</t>
+          <t>404352</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>411580</t>
+          <t>466951</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>54,22%</t>
+          <t>54,58%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>49,93%</t>
+          <t>50,41%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>58,48%</t>
+          <t>58,21%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -11245,32 +11245,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>626311</t>
+          <t>450661</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>522124</t>
+          <t>423831</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>767367</t>
+          <t>475624</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>67,23%</t>
+          <t>55,62%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>56,05%</t>
+          <t>52,3%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>82,38%</t>
+          <t>58,7%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -11280,32 +11280,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1007923</t>
+          <t>888489</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>898194</t>
+          <t>848209</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1214079</t>
+          <t>929470</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>61,63%</t>
+          <t>55,1%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>54,92%</t>
+          <t>52,6%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>74,24%</t>
+          <t>57,64%</t>
         </is>
       </c>
     </row>
@@ -11323,32 +11323,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>228338</t>
+          <t>264308</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>201848</t>
+          <t>238275</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>257676</t>
+          <t>297491</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>32,44%</t>
+          <t>32,95%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>28,68%</t>
+          <t>29,71%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>36,61%</t>
+          <t>37,09%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11358,32 +11358,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>214982</t>
+          <t>250695</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>115917</t>
+          <t>229972</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>288892</t>
+          <t>277208</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>30,94%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>12,44%</t>
+          <t>28,38%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>31,01%</t>
+          <t>34,21%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11393,32 +11393,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>443320</t>
+          <t>515003</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>287758</t>
+          <t>479064</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>523499</t>
+          <t>553054</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>27,11%</t>
+          <t>31,94%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>17,6%</t>
+          <t>29,71%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>32,01%</t>
+          <t>34,3%</t>
         </is>
       </c>
     </row>
@@ -11436,32 +11436,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>41517</t>
+          <t>43410</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>29125</t>
+          <t>30568</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>56475</t>
+          <t>58315</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>5,9%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11471,32 +11471,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>49816</t>
+          <t>59675</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>24759</t>
+          <t>47345</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>69652</t>
+          <t>73715</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>9,1%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11506,32 +11506,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>91333</t>
+          <t>103084</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>63814</t>
+          <t>85448</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>115890</t>
+          <t>123226</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>6,39%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>7,64%</t>
         </is>
       </c>
     </row>
@@ -11549,17 +11549,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>703816</t>
+          <t>802132</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>703816</t>
+          <t>802132</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>703816</t>
+          <t>802132</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11584,17 +11584,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>931546</t>
+          <t>810313</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>931546</t>
+          <t>810313</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>931546</t>
+          <t>810313</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11619,17 +11619,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1635362</t>
+          <t>1612444</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1635362</t>
+          <t>1612444</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1635362</t>
+          <t>1612444</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11666,32 +11666,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>34810</t>
+          <t>41132</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>23780</t>
+          <t>27808</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>50669</t>
+          <t>59014</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,97%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11701,32 +11701,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>47294</t>
+          <t>52685</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>34375</t>
+          <t>39950</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>65897</t>
+          <t>69325</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11736,32 +11736,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>82104</t>
+          <t>93817</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>65318</t>
+          <t>74399</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>105427</t>
+          <t>117128</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,56%</t>
         </is>
       </c>
     </row>
@@ -11779,32 +11779,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>525114</t>
+          <t>561744</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>492647</t>
+          <t>524572</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>557739</t>
+          <t>593484</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>56,72%</t>
+          <t>56,8%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>53,21%</t>
+          <t>53,04%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>60,24%</t>
+          <t>60,01%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11814,32 +11814,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>632461</t>
+          <t>616567</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>591481</t>
+          <t>585821</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>729075</t>
+          <t>644426</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>57,78%</t>
+          <t>55,12%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>54,04%</t>
+          <t>52,37%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>66,61%</t>
+          <t>57,61%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11849,32 +11849,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>1157575</t>
+          <t>1178312</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>1106830</t>
+          <t>1134342</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>1254379</t>
+          <t>1222848</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>57,29%</t>
+          <t>55,91%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>54,78%</t>
+          <t>53,82%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>62,09%</t>
+          <t>58,02%</t>
         </is>
       </c>
     </row>
@@ -11892,32 +11892,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>282490</t>
+          <t>297795</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>251107</t>
+          <t>269729</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>308669</t>
+          <t>328476</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>30,51%</t>
+          <t>30,11%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>27,12%</t>
+          <t>27,27%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>33,34%</t>
+          <t>33,21%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -11927,32 +11927,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>316602</t>
+          <t>342978</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>254529</t>
+          <t>317656</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>347346</t>
+          <t>370900</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>28,93%</t>
+          <t>30,66%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>28,4%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>31,73%</t>
+          <t>33,16%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -11962,32 +11962,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>599093</t>
+          <t>640772</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>534718</t>
+          <t>604978</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>645495</t>
+          <t>688922</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>29,65%</t>
+          <t>30,4%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>26,47%</t>
+          <t>28,7%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>31,95%</t>
+          <t>32,69%</t>
         </is>
       </c>
     </row>
@@ -12005,32 +12005,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>83451</t>
+          <t>88320</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>67933</t>
+          <t>71493</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>103076</t>
+          <t>109776</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>11,13%</t>
+          <t>11,1%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12040,32 +12040,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>98170</t>
+          <t>106380</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>77785</t>
+          <t>90434</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>116340</t>
+          <t>122856</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>9,51%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12075,32 +12075,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>181621</t>
+          <t>194700</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>154225</t>
+          <t>170436</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>207579</t>
+          <t>222751</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>8,99%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>8,09%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>10,27%</t>
+          <t>10,57%</t>
         </is>
       </c>
     </row>
@@ -12118,17 +12118,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>925865</t>
+          <t>988991</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>925865</t>
+          <t>988991</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>925865</t>
+          <t>988991</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12153,17 +12153,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>1094528</t>
+          <t>1118610</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1094528</t>
+          <t>1118610</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1094528</t>
+          <t>1118610</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12188,17 +12188,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>2020393</t>
+          <t>2107601</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2020393</t>
+          <t>2107601</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2020393</t>
+          <t>2107601</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12235,32 +12235,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>177409</t>
+          <t>192869</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>133866</t>
+          <t>163778</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>214795</t>
+          <t>231412</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -12270,32 +12270,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>194813</t>
+          <t>216972</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>159865</t>
+          <t>189944</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>228000</t>
+          <t>246454</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>5,33%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>6,61%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -12305,32 +12305,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>372222</t>
+          <t>409841</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>311437</t>
+          <t>367638</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>423865</t>
+          <t>457368</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>5,06%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>5,96%</t>
+          <t>6,3%</t>
         </is>
       </c>
     </row>
@@ -12348,32 +12348,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>1780563</t>
+          <t>1986101</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1374758</t>
+          <t>1922936</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>1938435</t>
+          <t>2054411</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>51,5%</t>
+          <t>56,27%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>39,77%</t>
+          <t>54,48%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>56,07%</t>
+          <t>58,2%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12383,32 +12383,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>2164707</t>
+          <t>2071429</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2041502</t>
+          <t>2012814</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2438407</t>
+          <t>2125296</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>59,21%</t>
+          <t>55,55%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>55,84%</t>
+          <t>53,98%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>66,69%</t>
+          <t>57,0%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12418,32 +12418,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>3945270</t>
+          <t>4057531</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>3499734</t>
+          <t>3974262</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>4217231</t>
+          <t>4143622</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>55,46%</t>
+          <t>55,9%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>49,2%</t>
+          <t>54,75%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>59,29%</t>
+          <t>57,09%</t>
         </is>
       </c>
     </row>
@@ -12461,32 +12461,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>1270288</t>
+          <t>1104938</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>1080759</t>
+          <t>1043726</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1784619</t>
+          <t>1164790</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>36,74%</t>
+          <t>31,3%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>31,26%</t>
+          <t>29,57%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>51,62%</t>
+          <t>33,0%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12496,32 +12496,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>1033635</t>
+          <t>1149366</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>844955</t>
+          <t>1098985</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>1123832</t>
+          <t>1199603</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>28,27%</t>
+          <t>30,82%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>23,11%</t>
+          <t>29,47%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>30,74%</t>
+          <t>32,17%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12531,32 +12531,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>2303922</t>
+          <t>2254305</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>2058154</t>
+          <t>2170489</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>2854078</t>
+          <t>2328751</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>32,39%</t>
+          <t>31,06%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>28,93%</t>
+          <t>29,9%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>40,12%</t>
+          <t>32,08%</t>
         </is>
       </c>
     </row>
@@ -12574,32 +12574,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>228937</t>
+          <t>245920</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>176716</t>
+          <t>217274</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>265619</t>
+          <t>279305</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,97%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -12609,32 +12609,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>263017</t>
+          <t>291074</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>210900</t>
+          <t>264588</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>295041</t>
+          <t>321341</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>7,19%</t>
+          <t>7,81%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>7,1%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -12644,32 +12644,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>491954</t>
+          <t>536994</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>424640</t>
+          <t>499471</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>540172</t>
+          <t>578753</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>5,97%</t>
+          <t>6,88%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>7,97%</t>
         </is>
       </c>
     </row>
@@ -12687,17 +12687,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>3457196</t>
+          <t>3529828</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>3457196</t>
+          <t>3529828</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>3457196</t>
+          <t>3529828</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -12722,17 +12722,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>3656172</t>
+          <t>3728842</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>3656172</t>
+          <t>3728842</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>3656172</t>
+          <t>3728842</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -12757,17 +12757,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>7113368</t>
+          <t>7258670</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>7113368</t>
+          <t>7258670</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>7113368</t>
+          <t>7258670</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
